--- a/Hodiny_Cap.xlsx
+++ b/Hodiny_Cap.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Týden 38" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Týden 39" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Týden 40" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Týden 41" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1648,7 +1649,7 @@
       <c r="B11" s="50" t="n"/>
       <c r="C11" s="61" t="n"/>
       <c r="D11" s="32" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="71" t="n"/>
@@ -1659,7 +1660,7 @@
         <v/>
       </c>
       <c r="Z11" s="91" t="n">
-        <v>45570</v>
+        <v>45574</v>
       </c>
     </row>
     <row r="12">
@@ -1688,10 +1689,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Chodur Radim</t>
+        </is>
+      </c>
       <c r="B13" s="50" t="n"/>
       <c r="C13" s="71" t="n"/>
-      <c r="D13" s="32" t="n"/>
+      <c r="D13" s="32" t="n">
+        <v>100</v>
+      </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="71" t="n"/>
       <c r="G13" s="71" t="n"/>
@@ -1699,6 +1706,9 @@
       <c r="I13" s="47">
         <f>SUM(B13+D13)</f>
         <v/>
+      </c>
+      <c r="Z13" s="91" t="n">
+        <v>45574</v>
       </c>
     </row>
     <row r="14">
@@ -5204,4 +5214,821 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S80"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15"/>
+  <cols>
+    <col width="28.5703125" customWidth="1" style="70" min="1" max="1"/>
+    <col width="5.7109375" customWidth="1" style="70" min="2" max="14"/>
+    <col width="5.7109375" customWidth="1" style="87" min="15" max="15"/>
+    <col width="13.140625" customWidth="1" style="70" min="16" max="16"/>
+    <col width="8.5703125" customWidth="1" style="70" min="17" max="102"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="74" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="B3" s="81">
+        <f>A80</f>
+        <v/>
+      </c>
+      <c r="C3" s="64" t="n"/>
+      <c r="D3" s="65" t="n"/>
+      <c r="E3" s="24" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="71" t="inlineStr">
+        <is>
+          <t>NÁZEV PROJEKTU : Ardo</t>
+        </is>
+      </c>
+      <c r="C4" s="64" t="n"/>
+      <c r="D4" s="64" t="n"/>
+      <c r="E4" s="64" t="n"/>
+      <c r="F4" s="64" t="n"/>
+      <c r="G4" s="64" t="n"/>
+      <c r="H4" s="64" t="n"/>
+      <c r="I4" s="64" t="n"/>
+      <c r="J4" s="64" t="n"/>
+      <c r="K4" s="64" t="n"/>
+      <c r="L4" s="64" t="n"/>
+      <c r="M4" s="64" t="n"/>
+      <c r="N4" s="64" t="n"/>
+      <c r="O4" s="64" t="n"/>
+      <c r="P4" s="65" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="74" t="n"/>
+      <c r="B5" s="83" t="inlineStr">
+        <is>
+          <t>Pondělí</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="n"/>
+      <c r="D5" s="84" t="inlineStr">
+        <is>
+          <t>Úterý</t>
+        </is>
+      </c>
+      <c r="E5" s="65" t="n"/>
+      <c r="F5" s="84" t="inlineStr">
+        <is>
+          <t>Středa</t>
+        </is>
+      </c>
+      <c r="G5" s="65" t="n"/>
+      <c r="H5" s="84" t="inlineStr">
+        <is>
+          <t>Čtvrtek</t>
+        </is>
+      </c>
+      <c r="I5" s="65" t="n"/>
+      <c r="J5" s="84" t="inlineStr">
+        <is>
+          <t>Pátek</t>
+        </is>
+      </c>
+      <c r="K5" s="65" t="n"/>
+      <c r="L5" s="84" t="inlineStr">
+        <is>
+          <t>Sobota</t>
+        </is>
+      </c>
+      <c r="M5" s="65" t="n"/>
+      <c r="N5" s="86" t="inlineStr">
+        <is>
+          <t>Neděle</t>
+        </is>
+      </c>
+      <c r="O5" s="65" t="n"/>
+      <c r="P5" s="66" t="inlineStr">
+        <is>
+          <t>HODINY CELKEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="70">
+      <c r="A6" s="73" t="inlineStr">
+        <is>
+          <t>Jméno pracovníka:</t>
+        </is>
+      </c>
+      <c r="B6" s="79">
+        <f>B80</f>
+        <v/>
+      </c>
+      <c r="C6" s="80" t="n"/>
+      <c r="D6" s="79">
+        <f>D80</f>
+        <v/>
+      </c>
+      <c r="E6" s="80" t="n"/>
+      <c r="F6" s="79">
+        <f>F80</f>
+        <v/>
+      </c>
+      <c r="G6" s="80" t="n"/>
+      <c r="H6" s="79">
+        <f>H80</f>
+        <v/>
+      </c>
+      <c r="I6" s="80" t="n"/>
+      <c r="J6" s="79">
+        <f>J80</f>
+        <v/>
+      </c>
+      <c r="K6" s="80" t="n"/>
+      <c r="L6" s="79">
+        <f>L80</f>
+        <v/>
+      </c>
+      <c r="M6" s="80" t="n"/>
+      <c r="N6" s="82">
+        <f>N80</f>
+        <v/>
+      </c>
+      <c r="O6" s="80" t="n"/>
+      <c r="P6" s="67" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="74" t="n"/>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D7" s="89" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E7" s="89" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F7" s="89" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G7" s="89" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H7" s="89" t="n"/>
+      <c r="I7" s="89" t="n"/>
+      <c r="J7" s="89" t="n"/>
+      <c r="K7" s="89" t="n"/>
+      <c r="L7" s="41" t="n"/>
+      <c r="M7" s="41" t="n"/>
+      <c r="N7" s="89" t="n"/>
+      <c r="O7" s="42" t="n"/>
+      <c r="P7" s="68" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>Čáp Jakub</t>
+        </is>
+      </c>
+      <c r="B8" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="77" t="n"/>
+      <c r="D8" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="77" t="n"/>
+      <c r="F8" s="85" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="77" t="n"/>
+      <c r="H8" s="85" t="n"/>
+      <c r="I8" s="77" t="n"/>
+      <c r="J8" s="85" t="n"/>
+      <c r="K8" s="77" t="n"/>
+      <c r="L8" s="85" t="n"/>
+      <c r="M8" s="77" t="n"/>
+      <c r="N8" s="78" t="n"/>
+      <c r="O8" s="77" t="n"/>
+      <c r="P8" s="39">
+        <f>SUM(B8:N8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>Chodur Radim</t>
+        </is>
+      </c>
+      <c r="B9" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="77" t="n"/>
+      <c r="D9" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="77" t="n"/>
+      <c r="F9" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="77" t="n"/>
+      <c r="H9" s="76" t="n"/>
+      <c r="I9" s="77" t="n"/>
+      <c r="J9" s="76" t="n"/>
+      <c r="K9" s="77" t="n"/>
+      <c r="L9" s="76" t="n"/>
+      <c r="M9" s="77" t="n"/>
+      <c r="N9" s="78" t="n"/>
+      <c r="O9" s="77" t="n"/>
+      <c r="P9" s="39">
+        <f>SUM(B9:N9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>Drdla Josef</t>
+        </is>
+      </c>
+      <c r="B10" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="77" t="n"/>
+      <c r="D10" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="77" t="n"/>
+      <c r="F10" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="77" t="n"/>
+      <c r="H10" s="88" t="n"/>
+      <c r="I10" s="77" t="n"/>
+      <c r="J10" s="76" t="n"/>
+      <c r="K10" s="77" t="n"/>
+      <c r="L10" s="76" t="n"/>
+      <c r="M10" s="77" t="n"/>
+      <c r="N10" s="76" t="n"/>
+      <c r="O10" s="77" t="n"/>
+      <c r="P10" s="39">
+        <f>SUM(B10:O10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Forster Michael Joseph</t>
+        </is>
+      </c>
+      <c r="B11" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="77" t="n"/>
+      <c r="D11" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="77" t="n"/>
+      <c r="F11" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="77" t="n"/>
+      <c r="H11" s="88" t="n"/>
+      <c r="I11" s="77" t="n"/>
+      <c r="J11" s="76" t="n"/>
+      <c r="K11" s="77" t="n"/>
+      <c r="L11" s="76" t="n"/>
+      <c r="M11" s="77" t="n"/>
+      <c r="N11" s="76" t="n"/>
+      <c r="O11" s="77" t="n"/>
+      <c r="P11" s="39">
+        <f>SUM(B11:O11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>Schmoranzer Martin</t>
+        </is>
+      </c>
+      <c r="B12" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="77" t="n"/>
+      <c r="D12" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="77" t="n"/>
+      <c r="F12" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="77" t="n"/>
+      <c r="H12" s="88" t="n"/>
+      <c r="I12" s="77" t="n"/>
+      <c r="J12" s="76" t="n"/>
+      <c r="K12" s="77" t="n"/>
+      <c r="L12" s="76" t="n"/>
+      <c r="M12" s="77" t="n"/>
+      <c r="N12" s="76" t="n"/>
+      <c r="O12" s="77" t="n"/>
+      <c r="P12" s="39">
+        <f>SUM(B12:O12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="76" t="n"/>
+      <c r="C13" s="76" t="n"/>
+      <c r="D13" s="76" t="n"/>
+      <c r="E13" s="76" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="88" t="n"/>
+      <c r="I13" s="88" t="n"/>
+      <c r="J13" s="76" t="n"/>
+      <c r="K13" s="76" t="n"/>
+      <c r="L13" s="76" t="n"/>
+      <c r="M13" s="76" t="n"/>
+      <c r="N13" s="76" t="n"/>
+      <c r="O13" s="78" t="n"/>
+      <c r="P13" s="39">
+        <f>SUM(B13:O13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="76" t="n"/>
+      <c r="C14" s="76" t="n"/>
+      <c r="D14" s="76" t="n"/>
+      <c r="E14" s="76" t="n"/>
+      <c r="F14" s="76" t="n"/>
+      <c r="G14" s="76" t="n"/>
+      <c r="H14" s="76" t="n"/>
+      <c r="I14" s="76" t="n"/>
+      <c r="J14" s="76" t="n"/>
+      <c r="K14" s="76" t="n"/>
+      <c r="L14" s="76" t="n"/>
+      <c r="M14" s="76" t="n"/>
+      <c r="N14" s="76" t="n"/>
+      <c r="O14" s="78" t="n"/>
+      <c r="P14" s="39">
+        <f>SUM(B14:O14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="76" t="n"/>
+      <c r="C15" s="76" t="n"/>
+      <c r="D15" s="76" t="n"/>
+      <c r="E15" s="76" t="n"/>
+      <c r="F15" s="76" t="n"/>
+      <c r="G15" s="76" t="n"/>
+      <c r="H15" s="76" t="n"/>
+      <c r="I15" s="76" t="n"/>
+      <c r="J15" s="76" t="n"/>
+      <c r="K15" s="76" t="n"/>
+      <c r="L15" s="76" t="n"/>
+      <c r="M15" s="76" t="n"/>
+      <c r="N15" s="76" t="n"/>
+      <c r="O15" s="78" t="n"/>
+      <c r="P15" s="39">
+        <f>SUM(B15:O15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="76" t="n"/>
+      <c r="C16" s="76" t="n"/>
+      <c r="D16" s="76" t="n"/>
+      <c r="E16" s="76" t="n"/>
+      <c r="F16" s="76" t="n"/>
+      <c r="G16" s="76" t="n"/>
+      <c r="H16" s="76" t="n"/>
+      <c r="I16" s="76" t="n"/>
+      <c r="J16" s="76" t="n"/>
+      <c r="K16" s="76" t="n"/>
+      <c r="L16" s="76" t="n"/>
+      <c r="M16" s="76" t="n"/>
+      <c r="N16" s="76" t="n"/>
+      <c r="O16" s="78" t="n"/>
+      <c r="P16" s="39">
+        <f>SUM(B16:O16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="38" t="n"/>
+      <c r="B17" s="76" t="n"/>
+      <c r="C17" s="76" t="n"/>
+      <c r="D17" s="76" t="n"/>
+      <c r="E17" s="76" t="n"/>
+      <c r="F17" s="76" t="n"/>
+      <c r="G17" s="76" t="n"/>
+      <c r="H17" s="76" t="n"/>
+      <c r="I17" s="76" t="n"/>
+      <c r="J17" s="76" t="n"/>
+      <c r="K17" s="76" t="n"/>
+      <c r="L17" s="76" t="n"/>
+      <c r="M17" s="76" t="n"/>
+      <c r="N17" s="76" t="n"/>
+      <c r="O17" s="78" t="n"/>
+      <c r="P17" s="39">
+        <f>SUM(B17:O17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="n"/>
+      <c r="B18" s="76" t="n"/>
+      <c r="C18" s="76" t="n"/>
+      <c r="D18" s="76" t="n"/>
+      <c r="E18" s="76" t="n"/>
+      <c r="F18" s="76" t="n"/>
+      <c r="G18" s="76" t="n"/>
+      <c r="H18" s="76" t="n"/>
+      <c r="I18" s="76" t="n"/>
+      <c r="J18" s="76" t="n"/>
+      <c r="K18" s="76" t="n"/>
+      <c r="L18" s="76" t="n"/>
+      <c r="M18" s="76" t="n"/>
+      <c r="N18" s="76" t="n"/>
+      <c r="O18" s="78" t="n"/>
+      <c r="P18" s="39">
+        <f>SUM(B18:O18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="n"/>
+      <c r="B19" s="76" t="n"/>
+      <c r="C19" s="76" t="n"/>
+      <c r="D19" s="76" t="n"/>
+      <c r="E19" s="76" t="n"/>
+      <c r="F19" s="76" t="n"/>
+      <c r="G19" s="76" t="n"/>
+      <c r="H19" s="76" t="n"/>
+      <c r="I19" s="76" t="n"/>
+      <c r="J19" s="76" t="n"/>
+      <c r="K19" s="76" t="n"/>
+      <c r="L19" s="76" t="n"/>
+      <c r="M19" s="76" t="n"/>
+      <c r="N19" s="76" t="n"/>
+      <c r="O19" s="78" t="n"/>
+      <c r="P19" s="39">
+        <f>SUM(B19:O19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="n"/>
+      <c r="B20" s="76" t="n"/>
+      <c r="C20" s="76" t="n"/>
+      <c r="D20" s="76" t="n"/>
+      <c r="E20" s="76" t="n"/>
+      <c r="F20" s="76" t="n"/>
+      <c r="G20" s="76" t="n"/>
+      <c r="H20" s="76" t="n"/>
+      <c r="I20" s="76" t="n"/>
+      <c r="J20" s="76" t="n"/>
+      <c r="K20" s="76" t="n"/>
+      <c r="L20" s="76" t="n"/>
+      <c r="M20" s="76" t="n"/>
+      <c r="N20" s="76" t="n"/>
+      <c r="O20" s="78" t="n"/>
+      <c r="P20" s="39">
+        <f>SUM(B20:O20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="n"/>
+      <c r="B21" s="76" t="n"/>
+      <c r="C21" s="76" t="n"/>
+      <c r="D21" s="76" t="n"/>
+      <c r="E21" s="76" t="n"/>
+      <c r="F21" s="76" t="n"/>
+      <c r="G21" s="76" t="n"/>
+      <c r="H21" s="76" t="n"/>
+      <c r="I21" s="76" t="n"/>
+      <c r="J21" s="76" t="n"/>
+      <c r="K21" s="76" t="n"/>
+      <c r="L21" s="76" t="n"/>
+      <c r="M21" s="76" t="n"/>
+      <c r="N21" s="76" t="n"/>
+      <c r="O21" s="78" t="n"/>
+      <c r="P21" s="39">
+        <f>SUM(B21:O21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="n"/>
+      <c r="B22" s="76" t="n"/>
+      <c r="C22" s="76" t="n"/>
+      <c r="D22" s="76" t="n"/>
+      <c r="E22" s="76" t="n"/>
+      <c r="F22" s="76" t="n"/>
+      <c r="G22" s="76" t="n"/>
+      <c r="H22" s="76" t="n"/>
+      <c r="I22" s="76" t="n"/>
+      <c r="J22" s="76" t="n"/>
+      <c r="K22" s="76" t="n"/>
+      <c r="L22" s="76" t="n"/>
+      <c r="M22" s="76" t="n"/>
+      <c r="N22" s="76" t="n"/>
+      <c r="O22" s="78" t="n"/>
+      <c r="P22" s="39">
+        <f>SUM(B22:O22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" s="16" t="n"/>
+      <c r="I23" s="16" t="n"/>
+      <c r="P23" s="5">
+        <f>SUM(P8:P22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Poznámky / Zálohy :</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>Přestávka od - do</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="n"/>
+      <c r="F24" s="1" t="n"/>
+      <c r="G24" s="21" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n"/>
+      <c r="D25" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="G25" s="22" t="n"/>
+      <c r="J25" s="69" t="inlineStr">
+        <is>
+          <t>HODINY PROSÍM VYPLŇOVAT V ČISTÉM ČASE, BEZ PŘESTÁVEK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n"/>
+      <c r="D26" s="71" t="n"/>
+      <c r="E26" s="71" t="n"/>
+      <c r="F26" s="71" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="26" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n"/>
+      <c r="D27" s="71" t="n"/>
+      <c r="E27" s="71" t="n"/>
+      <c r="F27" s="71" t="n"/>
+      <c r="G27" s="24" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
+      <c r="G28" s="24" t="n"/>
+    </row>
+    <row r="29">
+      <c r="J29" s="69" t="inlineStr">
+        <is>
+          <t>HODINY PROSÍM POSÍLAT TÝDNĚ NA EMAIL: hodiny@czechmontage.cz</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="90" t="inlineStr">
+        <is>
+          <t>Přejezdy z projektu na projekt - pouze pracovní cesty z jednoho projektu na druhý!</t>
+        </is>
+      </c>
+      <c r="B30" s="64" t="n"/>
+      <c r="C30" s="64" t="n"/>
+      <c r="D30" s="64" t="n"/>
+      <c r="E30" s="64" t="n"/>
+      <c r="F30" s="64" t="n"/>
+      <c r="G30" s="64" t="n"/>
+      <c r="H30" s="65" t="n"/>
+      <c r="I30" s="23" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Jméno pracovníka</t>
+        </is>
+      </c>
+      <c r="B31" s="71" t="inlineStr">
+        <is>
+          <t>Odkud</t>
+        </is>
+      </c>
+      <c r="C31" s="71" t="n"/>
+      <c r="D31" s="71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kam </t>
+        </is>
+      </c>
+      <c r="E31" s="71" t="n"/>
+      <c r="F31" s="71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kdy </t>
+        </is>
+      </c>
+      <c r="G31" s="71" t="n"/>
+      <c r="H31" s="71" t="inlineStr">
+        <is>
+          <t>Délka cesty</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="25" t="inlineStr">
+        <is>
+          <t>Km</t>
+        </is>
+      </c>
+      <c r="K31" s="25" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="n"/>
+      <c r="B32" s="45" t="n"/>
+      <c r="C32" s="45" t="n"/>
+      <c r="D32" s="45" t="n"/>
+      <c r="E32" s="45" t="n"/>
+      <c r="F32" s="46" t="n"/>
+      <c r="G32" s="46" t="n"/>
+      <c r="H32" s="71" t="n"/>
+      <c r="I32" s="24" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="n"/>
+      <c r="B33" s="45" t="n"/>
+      <c r="C33" s="45" t="n"/>
+      <c r="D33" s="45" t="n"/>
+      <c r="E33" s="45" t="n"/>
+      <c r="F33" s="46" t="n"/>
+      <c r="G33" s="46" t="n"/>
+      <c r="H33" s="71" t="n"/>
+      <c r="I33" s="24" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="n"/>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="29" t="n"/>
+      <c r="G34" s="29" t="n"/>
+      <c r="H34" s="71" t="n"/>
+      <c r="I34" s="24" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="24" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="43" t="inlineStr">
+        <is>
+          <t>Týden 41</t>
+        </is>
+      </c>
+      <c r="B80" s="36" t="inlineStr">
+        <is>
+          <t>07.10.2024</t>
+        </is>
+      </c>
+      <c r="C80" s="36" t="n"/>
+      <c r="D80" s="36" t="inlineStr">
+        <is>
+          <t>08.10.2024</t>
+        </is>
+      </c>
+      <c r="E80" s="36" t="n"/>
+      <c r="F80" s="36" t="inlineStr">
+        <is>
+          <t>09.10.2024</t>
+        </is>
+      </c>
+      <c r="G80" s="36" t="n"/>
+      <c r="H80" s="36" t="n"/>
+      <c r="I80" s="36" t="n"/>
+      <c r="J80" s="36" t="n"/>
+      <c r="K80" s="36" t="n"/>
+      <c r="L80" s="36" t="n"/>
+      <c r="M80" s="36" t="n"/>
+      <c r="N80" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="57">
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="J25:R25"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="J29:S29"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="B4:P4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Hodiny_Cap.xlsx
+++ b/Hodiny_Cap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cowley\Desktop\Programovani\prace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cowley\Desktop\Programovani\zal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E54516E-342D-410E-A723-065206EF5703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC8FD3A-9FF2-4CEE-96A2-9F12158157D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="18000" windowHeight="9810" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VZOR JAK VYPLNIT" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="Týden 39" sheetId="5" r:id="rId5"/>
     <sheet name="Týden 40" sheetId="6" r:id="rId6"/>
     <sheet name="Týden 41" sheetId="7" r:id="rId7"/>
+    <sheet name="Týden 42" sheetId="8" r:id="rId8"/>
+    <sheet name="Týden 43" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="100">
   <si>
     <t>Týden: 43</t>
   </si>
@@ -122,6 +124,9 @@
     <t>CZK</t>
   </si>
   <si>
+    <t>ZVB</t>
+  </si>
+  <si>
     <t>Jakub Čáp</t>
   </si>
   <si>
@@ -146,6 +151,9 @@
     <t>Říjen</t>
   </si>
   <si>
+    <t>NÁZEV PROJEKTU : LarFrost</t>
+  </si>
+  <si>
     <t>Úterý</t>
   </si>
   <si>
@@ -267,18 +275,85 @@
   </si>
   <si>
     <t>09.10.2024</t>
+  </si>
+  <si>
+    <t>10.10.2024</t>
+  </si>
+  <si>
+    <t>11.10.2024</t>
+  </si>
+  <si>
+    <t>12.10.2024</t>
+  </si>
+  <si>
+    <t>Týden 42</t>
+  </si>
+  <si>
+    <t>14.10.2024</t>
+  </si>
+  <si>
+    <t>15.10.2024</t>
+  </si>
+  <si>
+    <t>16.10.2024</t>
+  </si>
+  <si>
+    <t>17.10.2024</t>
+  </si>
+  <si>
+    <t>18.10.2024</t>
+  </si>
+  <si>
+    <t>19.10.2024</t>
+  </si>
+  <si>
+    <t>Schejbal Martin</t>
+  </si>
+  <si>
+    <t>Jakub</t>
+  </si>
+  <si>
+    <t>Malý František</t>
+  </si>
+  <si>
+    <t>Týden 43</t>
+  </si>
+  <si>
+    <t>21.10.2024</t>
+  </si>
+  <si>
+    <t>22.10.2024</t>
+  </si>
+  <si>
+    <t>23.10.2024</t>
+  </si>
+  <si>
+    <t>24.10.2024</t>
+  </si>
+  <si>
+    <t>25.10.2024</t>
+  </si>
+  <si>
+    <t>26.10.2024</t>
+  </si>
+  <si>
+    <t>Karel Jiří</t>
+  </si>
+  <si>
+    <t>Mrazák</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="d/m;@"/>
     <numFmt numFmtId="165" formatCode="#,##0\ [$€-1];[Red]\-#,##0\ [$€-1]"/>
     <numFmt numFmtId="166" formatCode="#,##0\ [$Kč-405]"/>
     <numFmt numFmtId="167" formatCode="#,##0\ [$€-1]"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0\ [$€-1]_-;\-* #,##0\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@_-"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -397,7 +472,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,6 +494,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,7 +663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -746,6 +827,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -774,45 +858,53 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1146,33 +1238,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="74"/>
+      <c r="A1" s="75"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
+      <c r="A2" s="71"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="65"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="66"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71" t="s">
+      <c r="A4" s="71"/>
+      <c r="B4" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="66"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
+      <c r="A5" s="75"/>
       <c r="B5" s="35" t="s">
         <v>2</v>
       </c>
@@ -1182,12 +1274,12 @@
       <c r="F5" s="54"/>
       <c r="G5" s="54"/>
       <c r="H5" s="54"/>
-      <c r="I5" s="66" t="s">
+      <c r="I5" s="67" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="10">
@@ -1199,10 +1291,10 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
-      <c r="I6" s="67"/>
+      <c r="I6" s="68"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
@@ -1212,7 +1304,7 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="68"/>
+      <c r="I7" s="69"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
@@ -1453,14 +1545,14 @@
       <c r="D25" s="9">
         <v>13</v>
       </c>
-      <c r="F25" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="70"/>
+      <c r="F25" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1479,14 +1571,14 @@
       <c r="A27" s="17"/>
       <c r="C27" s="52"/>
       <c r="D27" s="52"/>
-      <c r="F27" s="72" t="s">
+      <c r="F27" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="70"/>
-      <c r="K27" s="70"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
@@ -1494,24 +1586,24 @@
       <c r="D28" s="52"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F29" s="69" t="s">
+      <c r="F29" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
     </row>
     <row r="30" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="63" t="s">
+      <c r="A30" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="65"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="66"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
@@ -1590,7 +1682,7 @@
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="13.140625" customWidth="1"/>
-    <col min="3" max="7" width="10.42578125" customWidth="1"/>
+    <col min="3" max="7" width="10.28515625" customWidth="1"/>
     <col min="8" max="8" width="8.5703125" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
     <col min="10" max="24" width="8.5703125" customWidth="1"/>
@@ -1600,40 +1692,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="74"/>
+      <c r="A1" s="75"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
+      <c r="A2" s="71"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71" t="s">
+      <c r="A3" s="71"/>
+      <c r="B3" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="65"/>
+      <c r="C3" s="66"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71" t="s">
+      <c r="A4" s="71"/>
+      <c r="B4" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
+      <c r="A5" s="75"/>
       <c r="B5" s="35"/>
       <c r="C5" s="27"/>
       <c r="D5" s="54"/>
@@ -1641,31 +1733,31 @@
       <c r="F5" s="54"/>
       <c r="G5" s="54"/>
       <c r="H5" s="54"/>
-      <c r="I5" s="66" t="s">
+      <c r="I5" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="75" t="str">
+      <c r="B6" s="76" t="str">
         <f>B80</f>
         <v>Září</v>
       </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="75" t="str">
+      <c r="C6" s="66"/>
+      <c r="D6" s="76" t="str">
         <f>D80</f>
         <v>Říjen</v>
       </c>
-      <c r="E6" s="65"/>
+      <c r="E6" s="66"/>
       <c r="F6" s="28"/>
       <c r="G6" s="28"/>
       <c r="H6" s="28"/>
-      <c r="I6" s="67"/>
+      <c r="I6" s="68"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="14" t="s">
         <v>25</v>
       </c>
@@ -1678,14 +1770,16 @@
       <c r="E7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="14"/>
+      <c r="F7" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
-      <c r="I7" s="68"/>
+      <c r="I7" s="69"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="30">
         <v>100</v>
@@ -1693,17 +1787,17 @@
       <c r="C8" s="31"/>
       <c r="D8" s="32"/>
       <c r="E8" s="33"/>
-      <c r="F8" s="52"/>
+      <c r="F8" s="63"/>
       <c r="G8" s="52"/>
       <c r="H8" s="52"/>
       <c r="I8" s="47">
-        <f t="shared" ref="I8:I13" si="0">SUM(B8+D8)</f>
+        <f t="shared" ref="I8:I10" si="0">SUM(B8+D8)</f>
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="30">
         <v>140</v>
@@ -1711,7 +1805,7 @@
       <c r="C9" s="59"/>
       <c r="D9" s="32"/>
       <c r="E9" s="33"/>
-      <c r="F9" s="52"/>
+      <c r="F9" s="63"/>
       <c r="G9" s="52"/>
       <c r="H9" s="52"/>
       <c r="I9" s="47">
@@ -1724,7 +1818,7 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="30">
         <v>110</v>
@@ -1732,7 +1826,7 @@
       <c r="C10" s="31"/>
       <c r="D10" s="32"/>
       <c r="E10" s="60"/>
-      <c r="F10" s="52"/>
+      <c r="F10" s="63"/>
       <c r="G10" s="52"/>
       <c r="H10" s="52"/>
       <c r="I10" s="47">
@@ -1745,20 +1839,22 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="50"/>
       <c r="C11" s="61"/>
       <c r="D11" s="32">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E11" s="34"/>
-      <c r="F11" s="52"/>
+      <c r="F11" s="63">
+        <v>150</v>
+      </c>
       <c r="G11" s="52"/>
       <c r="H11" s="52"/>
       <c r="I11" s="47">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <f>SUM(B11+D11+F5)</f>
+        <v>400</v>
       </c>
       <c r="Z11" s="62">
         <v>45574</v>
@@ -1766,22 +1862,22 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="50">
         <v>100</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="32">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E12" s="60"/>
-      <c r="F12" s="52"/>
+      <c r="F12" s="63"/>
       <c r="G12" s="52"/>
       <c r="H12" s="52"/>
       <c r="I12" s="47">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <f>SUM(B12+D12+F12)</f>
+        <v>500</v>
       </c>
       <c r="Z12" s="62">
         <v>45569</v>
@@ -1789,20 +1885,22 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="50"/>
       <c r="C13" s="52"/>
       <c r="D13" s="32">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E13" s="34"/>
-      <c r="F13" s="52"/>
+      <c r="F13" s="63">
+        <v>100</v>
+      </c>
       <c r="G13" s="52"/>
       <c r="H13" s="52"/>
       <c r="I13" s="47">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <f>SUM(B13+D13+F13)</f>
+        <v>400</v>
       </c>
       <c r="Z13" s="62">
         <v>45574</v>
@@ -1814,7 +1912,7 @@
       <c r="C14" s="52"/>
       <c r="D14" s="32"/>
       <c r="E14" s="33"/>
-      <c r="F14" s="52"/>
+      <c r="F14" s="63"/>
       <c r="G14" s="52"/>
       <c r="H14" s="52"/>
       <c r="I14" s="47"/>
@@ -1825,7 +1923,7 @@
       <c r="C15" s="52"/>
       <c r="D15" s="32"/>
       <c r="E15" s="33"/>
-      <c r="F15" s="52"/>
+      <c r="F15" s="63"/>
       <c r="G15" s="52"/>
       <c r="H15" s="52"/>
       <c r="I15" s="47"/>
@@ -1836,7 +1934,7 @@
       <c r="C16" s="52"/>
       <c r="D16" s="32"/>
       <c r="E16" s="33"/>
-      <c r="F16" s="52"/>
+      <c r="F16" s="63"/>
       <c r="G16" s="52"/>
       <c r="H16" s="52"/>
       <c r="I16" s="47"/>
@@ -1847,7 +1945,7 @@
       <c r="C17" s="52"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33"/>
-      <c r="F17" s="52"/>
+      <c r="F17" s="63"/>
       <c r="G17" s="52"/>
       <c r="H17" s="52"/>
       <c r="I17" s="47"/>
@@ -1858,7 +1956,7 @@
       <c r="C18" s="52"/>
       <c r="D18" s="32"/>
       <c r="E18" s="33"/>
-      <c r="F18" s="52"/>
+      <c r="F18" s="63"/>
       <c r="G18" s="52"/>
       <c r="H18" s="52"/>
       <c r="I18" s="47"/>
@@ -1869,7 +1967,7 @@
       <c r="C19" s="52"/>
       <c r="D19" s="32"/>
       <c r="E19" s="33"/>
-      <c r="F19" s="52"/>
+      <c r="F19" s="63"/>
       <c r="G19" s="52"/>
       <c r="H19" s="52"/>
       <c r="I19" s="47"/>
@@ -1880,7 +1978,7 @@
       <c r="C20" s="52"/>
       <c r="D20" s="32"/>
       <c r="E20" s="33"/>
-      <c r="F20" s="52"/>
+      <c r="F20" s="63"/>
       <c r="G20" s="52"/>
       <c r="H20" s="52"/>
       <c r="I20" s="47"/>
@@ -1891,7 +1989,7 @@
       <c r="C21" s="52"/>
       <c r="D21" s="32"/>
       <c r="E21" s="33"/>
-      <c r="F21" s="52"/>
+      <c r="F21" s="63"/>
       <c r="G21" s="52"/>
       <c r="H21" s="52"/>
       <c r="I21" s="47"/>
@@ -1902,7 +2000,7 @@
       <c r="C22" s="52"/>
       <c r="D22" s="32"/>
       <c r="E22" s="33"/>
-      <c r="F22" s="52"/>
+      <c r="F22" s="63"/>
       <c r="G22" s="52"/>
       <c r="H22" s="52"/>
       <c r="I22" s="47"/>
@@ -1912,7 +2010,7 @@
       <c r="E23" s="16"/>
       <c r="I23" s="47">
         <f>SUM(I8:I22)</f>
-        <v>1150</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1924,12 +2022,12 @@
       <c r="A25" s="11"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
@@ -1953,20 +2051,20 @@
       <c r="D28" s="52"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="63"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="65"/>
+      <c r="A30" s="64"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="66"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
@@ -2003,24 +2101,24 @@
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F25:K25"/>
+    <mergeCell ref="D6:E6"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="F29:L29"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F25:K25"/>
-    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2039,77 +2137,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="74"/>
+      <c r="A1" s="75"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
+      <c r="A2" s="71"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="88" t="str">
+      <c r="A3" s="71"/>
+      <c r="B3" s="79" t="str">
         <f>A80</f>
         <v>Týden</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
       <c r="E3" s="24"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="90" t="s">
+      <c r="A5" s="75"/>
+      <c r="B5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="80" t="s">
+      <c r="C5" s="66"/>
+      <c r="D5" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="65"/>
-      <c r="J5" s="80" t="s">
+      <c r="E5" s="66"/>
+      <c r="F5" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="65"/>
-      <c r="L5" s="80" t="s">
+      <c r="G5" s="66"/>
+      <c r="H5" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="65"/>
-      <c r="N5" s="85" t="s">
+      <c r="I5" s="66"/>
+      <c r="J5" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66" t="s">
+      <c r="K5" s="66"/>
+      <c r="L5" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="66"/>
+      <c r="N5" s="86" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="82">
@@ -2142,15 +2240,15 @@
         <v>0</v>
       </c>
       <c r="M6" s="83"/>
-      <c r="N6" s="89">
+      <c r="N6" s="87">
         <f>N80</f>
         <v>0</v>
       </c>
       <c r="O6" s="83"/>
-      <c r="P6" s="67"/>
+      <c r="P6" s="68"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="41"/>
       <c r="C7" s="41"/>
       <c r="D7" s="48"/>
@@ -2165,26 +2263,26 @@
       <c r="M7" s="41"/>
       <c r="N7" s="48"/>
       <c r="O7" s="42"/>
-      <c r="P7" s="68"/>
+      <c r="P7" s="69"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="77"/>
+        <v>43</v>
+      </c>
+      <c r="B8" s="77"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="78"/>
+      <c r="N8" s="77"/>
+      <c r="O8" s="78"/>
       <c r="P8" s="39">
         <f>SUM(B8:N8)</f>
         <v>0</v>
@@ -2192,20 +2290,20 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="37"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="79"/>
-      <c r="M9" s="77"/>
-      <c r="N9" s="87"/>
-      <c r="O9" s="77"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="78"/>
       <c r="P9" s="39">
         <f>SUM(B9:N9)</f>
         <v>0</v>
@@ -2213,20 +2311,20 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="77"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="77"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="77"/>
+      <c r="O10" s="78"/>
       <c r="P10" s="39">
         <f t="shared" ref="P10:P22" si="0">SUM(B10:O10)</f>
         <v>0</v>
@@ -2234,20 +2332,20 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
-      <c r="B11" s="79"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="77"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="78"/>
       <c r="P11" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2255,20 +2353,20 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="77"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="78"/>
+      <c r="N12" s="77"/>
+      <c r="O12" s="78"/>
       <c r="P12" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2276,20 +2374,20 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="57"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="78"/>
+      <c r="N13" s="77"/>
+      <c r="O13" s="78"/>
       <c r="P13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2297,20 +2395,20 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="57"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="78"/>
       <c r="P14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2318,20 +2416,20 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="57"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="78"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="78"/>
       <c r="P15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2339,20 +2437,20 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="53"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="57"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="78"/>
       <c r="P16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2360,20 +2458,20 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="57"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="78"/>
       <c r="P17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2381,20 +2479,20 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="38"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="57"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="78"/>
+      <c r="N18" s="77"/>
+      <c r="O18" s="78"/>
       <c r="P18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2402,20 +2500,20 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="38"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="57"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="78"/>
       <c r="P19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2423,20 +2521,20 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="57"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="78"/>
       <c r="P20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2444,20 +2542,20 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="38"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="57"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="78"/>
       <c r="P21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2465,20 +2563,20 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="38"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="57"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="78"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="77"/>
+      <c r="M22" s="78"/>
+      <c r="N22" s="77"/>
+      <c r="O22" s="78"/>
       <c r="P22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2513,17 +2611,17 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="G25" s="22"/>
-      <c r="J25" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
+      <c r="J25" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
@@ -2556,30 +2654,30 @@
       <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="J29" s="69" t="s">
+      <c r="J29" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="84"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="65"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="66"/>
       <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -2587,23 +2685,23 @@
         <v>14</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C31" s="52"/>
       <c r="D31" s="52" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E31" s="52"/>
       <c r="F31" s="52" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G31" s="52"/>
       <c r="H31" s="52" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I31" s="24"/>
       <c r="J31" s="25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K31" s="25"/>
     </row>
@@ -2652,7 +2750,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B80" s="36"/>
       <c r="C80" s="36"/>
@@ -2669,64 +2767,134 @@
       <c r="N80" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="127">
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="J29:S29"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J25:R25"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A1:A5"/>
-    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="F5:G5"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B3:D3"/>
     <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="P5:P7"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="J29:S29"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="J25:R25"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="L12:M12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2745,77 +2913,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="74"/>
+      <c r="A1" s="75"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
+      <c r="A2" s="71"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="88" t="str">
+      <c r="A3" s="71"/>
+      <c r="B3" s="79" t="str">
         <f>A80</f>
         <v>Týden 38</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
       <c r="E3" s="24"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="90" t="s">
+      <c r="A5" s="75"/>
+      <c r="B5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="80" t="s">
+      <c r="C5" s="66"/>
+      <c r="D5" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="65"/>
-      <c r="J5" s="80" t="s">
+      <c r="E5" s="66"/>
+      <c r="F5" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="65"/>
-      <c r="L5" s="80" t="s">
+      <c r="G5" s="66"/>
+      <c r="H5" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="65"/>
-      <c r="N5" s="85" t="s">
+      <c r="I5" s="66"/>
+      <c r="J5" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66" t="s">
+      <c r="K5" s="66"/>
+      <c r="L5" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="66"/>
+      <c r="N5" s="86" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="82">
@@ -2848,15 +3016,15 @@
         <v>45556</v>
       </c>
       <c r="M6" s="83"/>
-      <c r="N6" s="89">
+      <c r="N6" s="87">
         <f>N80</f>
         <v>45557</v>
       </c>
       <c r="O6" s="83"/>
-      <c r="P6" s="67"/>
+      <c r="P6" s="68"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="41"/>
       <c r="C7" s="41"/>
       <c r="D7" s="48"/>
@@ -2864,57 +3032,57 @@
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J7" s="48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L7" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="41" t="s">
-        <v>50</v>
-      </c>
       <c r="N7" s="48" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O7" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="P7" s="68"/>
+        <v>55</v>
+      </c>
+      <c r="P7" s="69"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="86">
+        <v>43</v>
+      </c>
+      <c r="B8" s="77"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="89">
         <v>10.5</v>
       </c>
-      <c r="I8" s="77"/>
-      <c r="J8" s="86">
+      <c r="I8" s="78"/>
+      <c r="J8" s="89">
         <v>8.5</v>
       </c>
-      <c r="K8" s="77"/>
-      <c r="L8" s="86">
+      <c r="K8" s="78"/>
+      <c r="L8" s="89">
         <v>9.5</v>
       </c>
-      <c r="M8" s="77"/>
-      <c r="N8" s="87" t="s">
-        <v>53</v>
-      </c>
-      <c r="O8" s="77"/>
+      <c r="M8" s="78"/>
+      <c r="N8" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="78"/>
       <c r="P8" s="39">
         <f>SUM(B8:N8)</f>
         <v>28.5</v>
@@ -2922,30 +3090,30 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="79">
+        <v>29</v>
+      </c>
+      <c r="B9" s="77"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="77">
         <v>10.5</v>
       </c>
-      <c r="I9" s="77"/>
-      <c r="J9" s="79">
+      <c r="I9" s="78"/>
+      <c r="J9" s="77">
         <v>8.5</v>
       </c>
-      <c r="K9" s="77"/>
-      <c r="L9" s="79">
+      <c r="K9" s="78"/>
+      <c r="L9" s="77">
         <v>9.5</v>
       </c>
-      <c r="M9" s="77"/>
-      <c r="N9" s="87" t="s">
-        <v>53</v>
-      </c>
-      <c r="O9" s="77"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="78"/>
       <c r="P9" s="39">
         <f>SUM(B9:N9)</f>
         <v>28.5</v>
@@ -2953,20 +3121,20 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="77"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="77"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="77"/>
+      <c r="O10" s="78"/>
       <c r="P10" s="39">
         <f>SUM(B10:O10)</f>
         <v>0</v>
@@ -3253,17 +3421,17 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="G25" s="22"/>
-      <c r="J25" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
+      <c r="J25" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
@@ -3296,30 +3464,30 @@
       <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="J29" s="69" t="s">
+      <c r="J29" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="84"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="65"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="66"/>
       <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -3327,23 +3495,23 @@
         <v>14</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C31" s="52"/>
       <c r="D31" s="52" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E31" s="52"/>
       <c r="F31" s="52" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G31" s="52"/>
       <c r="H31" s="52" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I31" s="24"/>
       <c r="J31" s="25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K31" s="25"/>
     </row>
@@ -3392,7 +3560,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B80" s="36"/>
       <c r="C80" s="36"/>
@@ -3418,6 +3586,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J25:R25"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="J29:S29"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A1:A5"/>
@@ -3434,33 +3629,6 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="J29:S29"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J25:R25"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="P5:P7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3468,6 +3636,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
   <dimension ref="A1:S80"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3479,77 +3650,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="74"/>
+      <c r="A1" s="75"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
+      <c r="A2" s="71"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="88" t="str">
+      <c r="A3" s="71"/>
+      <c r="B3" s="79" t="str">
         <f>A80</f>
         <v>Týden 39</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
       <c r="E3" s="24"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="90" t="s">
+      <c r="A5" s="75"/>
+      <c r="B5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="80" t="s">
+      <c r="C5" s="66"/>
+      <c r="D5" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="65"/>
-      <c r="J5" s="80" t="s">
+      <c r="E5" s="66"/>
+      <c r="F5" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="65"/>
-      <c r="L5" s="80" t="s">
+      <c r="G5" s="66"/>
+      <c r="H5" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="65"/>
-      <c r="N5" s="85" t="s">
+      <c r="I5" s="66"/>
+      <c r="J5" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66" t="s">
+      <c r="K5" s="66"/>
+      <c r="L5" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="66"/>
+      <c r="N5" s="86" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="82">
@@ -3582,91 +3753,91 @@
         <v>45563</v>
       </c>
       <c r="M6" s="83"/>
-      <c r="N6" s="89">
+      <c r="N6" s="87">
         <f>N80</f>
         <v>45564</v>
       </c>
       <c r="O6" s="83"/>
-      <c r="P6" s="67"/>
+      <c r="P6" s="68"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L7" s="41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N7" s="48" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O7" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="P7" s="68"/>
+        <v>55</v>
+      </c>
+      <c r="P7" s="69"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="79">
+        <v>43</v>
+      </c>
+      <c r="B8" s="77">
         <v>7</v>
       </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="79">
+      <c r="C8" s="78"/>
+      <c r="D8" s="77">
         <v>10.5</v>
       </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="86">
-        <v>10</v>
-      </c>
-      <c r="G8" s="77"/>
-      <c r="H8" s="86">
-        <v>10</v>
-      </c>
-      <c r="I8" s="77"/>
-      <c r="J8" s="86">
-        <v>10</v>
-      </c>
-      <c r="K8" s="77"/>
-      <c r="L8" s="86">
+      <c r="E8" s="78"/>
+      <c r="F8" s="89">
+        <v>10</v>
+      </c>
+      <c r="G8" s="78"/>
+      <c r="H8" s="89">
+        <v>10</v>
+      </c>
+      <c r="I8" s="78"/>
+      <c r="J8" s="89">
+        <v>10</v>
+      </c>
+      <c r="K8" s="78"/>
+      <c r="L8" s="89">
         <v>8</v>
       </c>
-      <c r="M8" s="77"/>
-      <c r="N8" s="87" t="s">
-        <v>53</v>
-      </c>
-      <c r="O8" s="77"/>
+      <c r="M8" s="78"/>
+      <c r="N8" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="78"/>
       <c r="P8" s="39">
         <f>SUM(B8:N8)</f>
         <v>55.5</v>
@@ -3674,36 +3845,36 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="79">
+        <v>33</v>
+      </c>
+      <c r="B9" s="77">
         <v>9</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="79">
+      <c r="C9" s="78"/>
+      <c r="D9" s="77">
         <v>10.5</v>
       </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="79">
-        <v>10</v>
-      </c>
-      <c r="G9" s="77"/>
-      <c r="H9" s="79">
-        <v>10</v>
-      </c>
-      <c r="I9" s="77"/>
-      <c r="J9" s="79">
-        <v>10</v>
-      </c>
-      <c r="K9" s="77"/>
-      <c r="L9" s="79">
+      <c r="E9" s="78"/>
+      <c r="F9" s="77">
+        <v>10</v>
+      </c>
+      <c r="G9" s="78"/>
+      <c r="H9" s="77">
+        <v>10</v>
+      </c>
+      <c r="I9" s="78"/>
+      <c r="J9" s="77">
+        <v>10</v>
+      </c>
+      <c r="K9" s="78"/>
+      <c r="L9" s="77">
         <v>8</v>
       </c>
-      <c r="M9" s="77"/>
-      <c r="N9" s="87" t="s">
-        <v>53</v>
-      </c>
-      <c r="O9" s="77"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="78"/>
       <c r="P9" s="39">
         <f>SUM(B9:N9)</f>
         <v>57.5</v>
@@ -3711,36 +3882,36 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="79">
+        <v>31</v>
+      </c>
+      <c r="B10" s="77">
         <v>9</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="79">
+      <c r="C10" s="78"/>
+      <c r="D10" s="77">
         <v>10.5</v>
       </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="79">
-        <v>10</v>
-      </c>
-      <c r="G10" s="77"/>
-      <c r="H10" s="81">
-        <v>10</v>
-      </c>
-      <c r="I10" s="77"/>
-      <c r="J10" s="79">
-        <v>10</v>
-      </c>
-      <c r="K10" s="77"/>
-      <c r="L10" s="79">
+      <c r="E10" s="78"/>
+      <c r="F10" s="77">
+        <v>10</v>
+      </c>
+      <c r="G10" s="78"/>
+      <c r="H10" s="90">
+        <v>10</v>
+      </c>
+      <c r="I10" s="78"/>
+      <c r="J10" s="77">
+        <v>10</v>
+      </c>
+      <c r="K10" s="78"/>
+      <c r="L10" s="77">
         <v>8</v>
       </c>
-      <c r="M10" s="77"/>
-      <c r="N10" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="O10" s="77"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="78"/>
       <c r="P10" s="39">
         <f>SUM(B10:O10)</f>
         <v>57.5</v>
@@ -4027,17 +4198,17 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="G25" s="22"/>
-      <c r="J25" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
+      <c r="J25" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
@@ -4070,30 +4241,30 @@
       <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="J29" s="69" t="s">
+      <c r="J29" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="84"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="65"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="66"/>
       <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -4101,43 +4272,43 @@
         <v>14</v>
       </c>
       <c r="B31" s="58" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C31" s="58"/>
       <c r="D31" s="52" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E31" s="52"/>
       <c r="F31" s="52" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G31" s="52"/>
       <c r="H31" s="52" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I31" s="24"/>
       <c r="J31" s="25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K31" s="25"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C32" s="45"/>
       <c r="D32" s="45" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E32" s="45"/>
       <c r="F32" s="46">
         <v>45558</v>
       </c>
       <c r="G32" s="46" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H32" s="52"/>
       <c r="I32" s="24"/>
@@ -4178,7 +4349,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B80" s="36">
         <v>45558</v>
@@ -4210,6 +4381,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J25:R25"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="J29:S29"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A1:A5"/>
@@ -4226,33 +4424,6 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="J29:S29"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J25:R25"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="P5:P7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4271,77 +4442,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="74"/>
+      <c r="A1" s="75"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
+      <c r="A2" s="71"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="88" t="str">
+      <c r="A3" s="71"/>
+      <c r="B3" s="79" t="str">
         <f>A80</f>
         <v>Týden 40</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
       <c r="E3" s="24"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="90" t="s">
+      <c r="A5" s="75"/>
+      <c r="B5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="80" t="s">
+      <c r="C5" s="66"/>
+      <c r="D5" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="65"/>
-      <c r="J5" s="80" t="s">
+      <c r="E5" s="66"/>
+      <c r="F5" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="65"/>
-      <c r="L5" s="80" t="s">
+      <c r="G5" s="66"/>
+      <c r="H5" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="65"/>
-      <c r="N5" s="85" t="s">
+      <c r="I5" s="66"/>
+      <c r="J5" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66" t="s">
+      <c r="K5" s="66"/>
+      <c r="L5" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="66"/>
+      <c r="N5" s="86" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="82" t="str">
@@ -4374,85 +4545,91 @@
         <v>05.10.2024</v>
       </c>
       <c r="M6" s="83"/>
-      <c r="N6" s="89">
+      <c r="N6" s="87">
         <f>N80</f>
-        <v>0</v>
+        <v>45571</v>
       </c>
       <c r="O6" s="83"/>
-      <c r="P6" s="67"/>
+      <c r="P6" s="68"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L7" s="41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="N7" s="48"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="68"/>
+        <v>65</v>
+      </c>
+      <c r="N7" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="69"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="79">
-        <v>10</v>
-      </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="79">
-        <v>10</v>
-      </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="86">
-        <v>10</v>
-      </c>
-      <c r="G8" s="77"/>
-      <c r="H8" s="86">
-        <v>10</v>
-      </c>
-      <c r="I8" s="77"/>
-      <c r="J8" s="86">
-        <v>10</v>
-      </c>
-      <c r="K8" s="77"/>
-      <c r="L8" s="86">
+        <v>43</v>
+      </c>
+      <c r="B8" s="77">
+        <v>10</v>
+      </c>
+      <c r="C8" s="78"/>
+      <c r="D8" s="77">
+        <v>10</v>
+      </c>
+      <c r="E8" s="78"/>
+      <c r="F8" s="89">
+        <v>10</v>
+      </c>
+      <c r="G8" s="78"/>
+      <c r="H8" s="89">
+        <v>10</v>
+      </c>
+      <c r="I8" s="78"/>
+      <c r="J8" s="89">
+        <v>10</v>
+      </c>
+      <c r="K8" s="78"/>
+      <c r="L8" s="89">
         <v>8</v>
       </c>
-      <c r="M8" s="77"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="77"/>
+      <c r="M8" s="78"/>
+      <c r="N8" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="78"/>
       <c r="P8" s="39">
         <f>SUM(B8:N8)</f>
         <v>58</v>
@@ -4460,34 +4637,36 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="79">
-        <v>10</v>
-      </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="79">
-        <v>10</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="79">
-        <v>10</v>
-      </c>
-      <c r="G9" s="77"/>
-      <c r="H9" s="79">
-        <v>10</v>
-      </c>
-      <c r="I9" s="77"/>
-      <c r="J9" s="79">
-        <v>10</v>
-      </c>
-      <c r="K9" s="77"/>
-      <c r="L9" s="79">
+        <v>33</v>
+      </c>
+      <c r="B9" s="77">
+        <v>10</v>
+      </c>
+      <c r="C9" s="78"/>
+      <c r="D9" s="77">
+        <v>10</v>
+      </c>
+      <c r="E9" s="78"/>
+      <c r="F9" s="77">
+        <v>10</v>
+      </c>
+      <c r="G9" s="78"/>
+      <c r="H9" s="77">
+        <v>10</v>
+      </c>
+      <c r="I9" s="78"/>
+      <c r="J9" s="77">
+        <v>10</v>
+      </c>
+      <c r="K9" s="78"/>
+      <c r="L9" s="77">
         <v>8</v>
       </c>
-      <c r="M9" s="77"/>
-      <c r="N9" s="87"/>
-      <c r="O9" s="77"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="78"/>
       <c r="P9" s="39">
         <f>SUM(B9:N9)</f>
         <v>58</v>
@@ -4495,34 +4674,36 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="79">
-        <v>10</v>
-      </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="79">
-        <v>10</v>
-      </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="79">
-        <v>10</v>
-      </c>
-      <c r="G10" s="77"/>
-      <c r="H10" s="81">
-        <v>10</v>
-      </c>
-      <c r="I10" s="77"/>
-      <c r="J10" s="79">
-        <v>10</v>
-      </c>
-      <c r="K10" s="77"/>
-      <c r="L10" s="79">
+        <v>31</v>
+      </c>
+      <c r="B10" s="77">
+        <v>10</v>
+      </c>
+      <c r="C10" s="78"/>
+      <c r="D10" s="77">
+        <v>10</v>
+      </c>
+      <c r="E10" s="78"/>
+      <c r="F10" s="77">
+        <v>10</v>
+      </c>
+      <c r="G10" s="78"/>
+      <c r="H10" s="90">
+        <v>10</v>
+      </c>
+      <c r="I10" s="78"/>
+      <c r="J10" s="77">
+        <v>10</v>
+      </c>
+      <c r="K10" s="78"/>
+      <c r="L10" s="77">
         <v>8</v>
       </c>
-      <c r="M10" s="77"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="77"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="78"/>
       <c r="P10" s="39">
         <f t="shared" ref="P10:P22" si="0">SUM(B10:O10)</f>
         <v>58</v>
@@ -4530,34 +4711,36 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="79">
-        <v>10</v>
-      </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="79">
-        <v>10</v>
-      </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="76">
-        <v>10</v>
-      </c>
-      <c r="G11" s="77"/>
-      <c r="H11" s="81">
-        <v>10</v>
-      </c>
-      <c r="I11" s="77"/>
-      <c r="J11" s="79">
-        <v>10</v>
-      </c>
-      <c r="K11" s="77"/>
-      <c r="L11" s="79">
+        <v>66</v>
+      </c>
+      <c r="B11" s="77">
+        <v>10</v>
+      </c>
+      <c r="C11" s="78"/>
+      <c r="D11" s="77">
+        <v>10</v>
+      </c>
+      <c r="E11" s="78"/>
+      <c r="F11" s="91">
+        <v>10</v>
+      </c>
+      <c r="G11" s="78"/>
+      <c r="H11" s="90">
+        <v>10</v>
+      </c>
+      <c r="I11" s="78"/>
+      <c r="J11" s="77">
+        <v>10</v>
+      </c>
+      <c r="K11" s="78"/>
+      <c r="L11" s="77">
         <v>8</v>
       </c>
-      <c r="M11" s="77"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="77"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" s="78"/>
       <c r="P11" s="39">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -4565,34 +4748,36 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="79">
-        <v>10</v>
-      </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="79">
-        <v>10</v>
-      </c>
-      <c r="E12" s="77"/>
-      <c r="F12" s="76">
-        <v>10</v>
-      </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="81">
-        <v>10</v>
-      </c>
-      <c r="I12" s="77"/>
-      <c r="J12" s="79">
-        <v>10</v>
-      </c>
-      <c r="K12" s="77"/>
-      <c r="L12" s="79">
-        <v>0</v>
-      </c>
-      <c r="M12" s="77"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="77"/>
+        <v>32</v>
+      </c>
+      <c r="B12" s="77">
+        <v>10</v>
+      </c>
+      <c r="C12" s="78"/>
+      <c r="D12" s="77">
+        <v>10</v>
+      </c>
+      <c r="E12" s="78"/>
+      <c r="F12" s="91">
+        <v>10</v>
+      </c>
+      <c r="G12" s="78"/>
+      <c r="H12" s="90">
+        <v>10</v>
+      </c>
+      <c r="I12" s="78"/>
+      <c r="J12" s="77">
+        <v>10</v>
+      </c>
+      <c r="K12" s="78"/>
+      <c r="L12" s="77">
+        <v>0</v>
+      </c>
+      <c r="M12" s="78"/>
+      <c r="N12" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="78"/>
       <c r="P12" s="39">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -4837,17 +5022,17 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="G25" s="22"/>
-      <c r="J25" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
+      <c r="J25" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
@@ -4880,30 +5065,30 @@
       <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="J29" s="69" t="s">
+      <c r="J29" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="84"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="65"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="66"/>
       <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -4911,36 +5096,36 @@
         <v>14</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C31" s="52"/>
       <c r="D31" s="52" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E31" s="52"/>
       <c r="F31" s="52" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G31" s="52"/>
       <c r="H31" s="52" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I31" s="24"/>
       <c r="J31" s="25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K31" s="25"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C32" s="45"/>
       <c r="D32" s="45" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E32" s="45"/>
       <c r="F32" s="46">
@@ -4953,13 +5138,15 @@
       <c r="K32" s="25"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
+      <c r="A33" s="17" t="s">
+        <v>31</v>
+      </c>
       <c r="B33" s="45" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C33" s="45"/>
       <c r="D33" s="45" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E33" s="45"/>
       <c r="F33" s="46">
@@ -4990,36 +5177,79 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C80" s="36"/>
       <c r="D80" s="36" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E80" s="36"/>
       <c r="F80" s="36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G80" s="36"/>
       <c r="H80" s="36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I80" s="36"/>
       <c r="J80" s="36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K80" s="36"/>
       <c r="L80" s="36" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M80" s="36"/>
-      <c r="N80" s="36"/>
+      <c r="N80" s="36">
+        <v>45571</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="J25:R25"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="J29:S29"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A1:A5"/>
@@ -5036,47 +5266,6 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="P5:P7"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="J29:S29"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="J25:R25"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="L12:M12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5095,77 +5284,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="74"/>
+      <c r="A1" s="75"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
+      <c r="A2" s="71"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="88" t="str">
+      <c r="A3" s="71"/>
+      <c r="B3" s="79" t="str">
         <f>A80</f>
         <v>Týden 41</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
       <c r="E3" s="24"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="90" t="s">
+      <c r="A5" s="75"/>
+      <c r="B5" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="80" t="s">
+      <c r="C5" s="66"/>
+      <c r="D5" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="65"/>
-      <c r="J5" s="80" t="s">
+      <c r="E5" s="66"/>
+      <c r="F5" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="65"/>
-      <c r="L5" s="80" t="s">
+      <c r="G5" s="66"/>
+      <c r="H5" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="65"/>
-      <c r="N5" s="85" t="s">
+      <c r="I5" s="66"/>
+      <c r="J5" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66" t="s">
+      <c r="K5" s="66"/>
+      <c r="L5" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="66"/>
+      <c r="N5" s="86" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="82" t="str">
@@ -5183,201 +5372,257 @@
         <v>09.10.2024</v>
       </c>
       <c r="G6" s="83"/>
-      <c r="H6" s="82">
+      <c r="H6" s="82" t="str">
         <f>H80</f>
-        <v>0</v>
+        <v>10.10.2024</v>
       </c>
       <c r="I6" s="83"/>
-      <c r="J6" s="82">
+      <c r="J6" s="82" t="str">
         <f>J80</f>
-        <v>0</v>
+        <v>11.10.2024</v>
       </c>
       <c r="K6" s="83"/>
-      <c r="L6" s="82">
+      <c r="L6" s="82" t="str">
         <f>L80</f>
-        <v>0</v>
+        <v>12.10.2024</v>
       </c>
       <c r="M6" s="83"/>
-      <c r="N6" s="89">
+      <c r="N6" s="87">
         <f>N80</f>
         <v>0</v>
       </c>
       <c r="O6" s="83"/>
-      <c r="P6" s="67"/>
+      <c r="P6" s="68"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="68"/>
+        <v>52</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="41">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="N7" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="69"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="79">
-        <v>10</v>
-      </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="79">
-        <v>10</v>
-      </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="86">
-        <v>10</v>
-      </c>
-      <c r="G8" s="77"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="77"/>
+        <v>43</v>
+      </c>
+      <c r="B8" s="77">
+        <v>10</v>
+      </c>
+      <c r="C8" s="78"/>
+      <c r="D8" s="77">
+        <v>10</v>
+      </c>
+      <c r="E8" s="78"/>
+      <c r="F8" s="89">
+        <v>10</v>
+      </c>
+      <c r="G8" s="78"/>
+      <c r="H8" s="89">
+        <v>10</v>
+      </c>
+      <c r="I8" s="78"/>
+      <c r="J8" s="89">
+        <v>9</v>
+      </c>
+      <c r="K8" s="78"/>
+      <c r="L8" s="89">
+        <v>0</v>
+      </c>
+      <c r="M8" s="78"/>
+      <c r="N8" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="78"/>
       <c r="P8" s="39">
         <f>SUM(B8:N8)</f>
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="79">
-        <v>10</v>
-      </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="79">
-        <v>10</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="79">
-        <v>10</v>
-      </c>
-      <c r="G9" s="77"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="79"/>
-      <c r="M9" s="77"/>
-      <c r="N9" s="87"/>
-      <c r="O9" s="77"/>
+        <v>33</v>
+      </c>
+      <c r="B9" s="77">
+        <v>10</v>
+      </c>
+      <c r="C9" s="78"/>
+      <c r="D9" s="77">
+        <v>10</v>
+      </c>
+      <c r="E9" s="78"/>
+      <c r="F9" s="77">
+        <v>10</v>
+      </c>
+      <c r="G9" s="78"/>
+      <c r="H9" s="77">
+        <v>10</v>
+      </c>
+      <c r="I9" s="78"/>
+      <c r="J9" s="77">
+        <v>10</v>
+      </c>
+      <c r="K9" s="78"/>
+      <c r="L9" s="77">
+        <v>8</v>
+      </c>
+      <c r="M9" s="78"/>
+      <c r="N9" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="78"/>
       <c r="P9" s="39">
         <f>SUM(B9:N9)</f>
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="79">
-        <v>10</v>
-      </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="79">
-        <v>10</v>
-      </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="79">
-        <v>10</v>
-      </c>
-      <c r="G10" s="77"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="77"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="77"/>
+        <v>31</v>
+      </c>
+      <c r="B10" s="77">
+        <v>10</v>
+      </c>
+      <c r="C10" s="78"/>
+      <c r="D10" s="77">
+        <v>10</v>
+      </c>
+      <c r="E10" s="78"/>
+      <c r="F10" s="77">
+        <v>10</v>
+      </c>
+      <c r="G10" s="78"/>
+      <c r="H10" s="90">
+        <v>10</v>
+      </c>
+      <c r="I10" s="78"/>
+      <c r="J10" s="77">
+        <v>10</v>
+      </c>
+      <c r="K10" s="78"/>
+      <c r="L10" s="77">
+        <v>8</v>
+      </c>
+      <c r="M10" s="78"/>
+      <c r="N10" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="78"/>
       <c r="P10" s="39">
         <f t="shared" ref="P10:P22" si="0">SUM(B10:O10)</f>
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="79">
-        <v>10</v>
-      </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="79">
-        <v>10</v>
-      </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="76">
-        <v>10</v>
-      </c>
-      <c r="G11" s="77"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="77"/>
+        <v>66</v>
+      </c>
+      <c r="B11" s="77">
+        <v>10</v>
+      </c>
+      <c r="C11" s="78"/>
+      <c r="D11" s="77">
+        <v>10</v>
+      </c>
+      <c r="E11" s="78"/>
+      <c r="F11" s="91">
+        <v>10</v>
+      </c>
+      <c r="G11" s="78"/>
+      <c r="H11" s="90">
+        <v>10</v>
+      </c>
+      <c r="I11" s="78"/>
+      <c r="J11" s="77">
+        <v>10</v>
+      </c>
+      <c r="K11" s="78"/>
+      <c r="L11" s="77">
+        <v>8</v>
+      </c>
+      <c r="M11" s="78"/>
+      <c r="N11" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" s="78"/>
       <c r="P11" s="39">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="79">
-        <v>10</v>
-      </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="79">
-        <v>10</v>
-      </c>
-      <c r="E12" s="77"/>
-      <c r="F12" s="76">
-        <v>10</v>
-      </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="77"/>
+        <v>32</v>
+      </c>
+      <c r="B12" s="77">
+        <v>10</v>
+      </c>
+      <c r="C12" s="78"/>
+      <c r="D12" s="77">
+        <v>10</v>
+      </c>
+      <c r="E12" s="78"/>
+      <c r="F12" s="91">
+        <v>10</v>
+      </c>
+      <c r="G12" s="78"/>
+      <c r="H12" s="90">
+        <v>10</v>
+      </c>
+      <c r="I12" s="78"/>
+      <c r="J12" s="77">
+        <v>10</v>
+      </c>
+      <c r="K12" s="78"/>
+      <c r="L12" s="77">
+        <v>8</v>
+      </c>
+      <c r="M12" s="78"/>
+      <c r="N12" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="78"/>
       <c r="P12" s="39">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -5595,7 +5840,7 @@
       <c r="I23" s="16"/>
       <c r="P23" s="5">
         <f>SUM(P8:P22)</f>
-        <v>150</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -5619,17 +5864,17 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="G25" s="22"/>
-      <c r="J25" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
+      <c r="J25" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
@@ -5662,30 +5907,30 @@
       <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="J29" s="69" t="s">
+      <c r="J29" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="84"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="65"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="66"/>
       <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -5693,23 +5938,23 @@
         <v>14</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C31" s="52"/>
       <c r="D31" s="52" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E31" s="52"/>
       <c r="F31" s="52" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G31" s="52"/>
       <c r="H31" s="52" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I31" s="24"/>
       <c r="J31" s="25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K31" s="25"/>
     </row>
@@ -5758,30 +6003,77 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C80" s="36"/>
       <c r="D80" s="36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E80" s="36"/>
       <c r="F80" s="36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
+      <c r="H80" s="36" t="s">
+        <v>78</v>
+      </c>
       <c r="I80" s="36"/>
-      <c r="J80" s="36"/>
+      <c r="J80" s="36" t="s">
+        <v>79</v>
+      </c>
       <c r="K80" s="36"/>
-      <c r="L80" s="36"/>
+      <c r="L80" s="36" t="s">
+        <v>80</v>
+      </c>
       <c r="M80" s="36"/>
       <c r="N80" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="J25:R25"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="J29:S29"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A1:A5"/>
@@ -5798,6 +6090,801 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H8:I8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:S80"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="14" width="5.7109375" customWidth="1"/>
+    <col min="15" max="15" width="5.7109375" style="56" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" customWidth="1"/>
+    <col min="17" max="102" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="75"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="71"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="71"/>
+      <c r="B3" s="79" t="str">
+        <f>A80</f>
+        <v>Týden 42</v>
+      </c>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="24"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="71"/>
+      <c r="B4" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="75"/>
+      <c r="B5" s="80" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="66"/>
+      <c r="D5" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="66"/>
+      <c r="F5" s="81" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="66"/>
+      <c r="H5" s="81" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="66"/>
+      <c r="J5" s="81" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="66"/>
+      <c r="L5" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="66"/>
+      <c r="N5" s="86" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="82" t="str">
+        <f>B80</f>
+        <v>14.10.2024</v>
+      </c>
+      <c r="C6" s="83"/>
+      <c r="D6" s="82" t="str">
+        <f>D80</f>
+        <v>15.10.2024</v>
+      </c>
+      <c r="E6" s="83"/>
+      <c r="F6" s="82" t="str">
+        <f>F80</f>
+        <v>16.10.2024</v>
+      </c>
+      <c r="G6" s="83"/>
+      <c r="H6" s="82" t="str">
+        <f>H80</f>
+        <v>17.10.2024</v>
+      </c>
+      <c r="I6" s="83"/>
+      <c r="J6" s="82" t="str">
+        <f>J80</f>
+        <v>18.10.2024</v>
+      </c>
+      <c r="K6" s="83"/>
+      <c r="L6" s="82" t="str">
+        <f>L80</f>
+        <v>19.10.2024</v>
+      </c>
+      <c r="M6" s="83"/>
+      <c r="N6" s="87">
+        <f>N80</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="83"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="94" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="75"/>
+      <c r="B7" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="N7" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="69"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="77">
+        <v>10</v>
+      </c>
+      <c r="C8" s="78"/>
+      <c r="D8" s="77">
+        <v>10</v>
+      </c>
+      <c r="E8" s="78"/>
+      <c r="F8" s="89">
+        <v>10</v>
+      </c>
+      <c r="G8" s="78"/>
+      <c r="H8" s="89">
+        <v>10</v>
+      </c>
+      <c r="I8" s="78"/>
+      <c r="J8" s="89">
+        <v>10</v>
+      </c>
+      <c r="K8" s="78"/>
+      <c r="L8" s="95">
+        <v>8</v>
+      </c>
+      <c r="M8" s="93"/>
+      <c r="N8" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="78"/>
+      <c r="P8" s="39">
+        <f>SUM(B8:N8)</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="77">
+        <v>10</v>
+      </c>
+      <c r="C9" s="78"/>
+      <c r="D9" s="77">
+        <v>10</v>
+      </c>
+      <c r="E9" s="78"/>
+      <c r="F9" s="77">
+        <v>10</v>
+      </c>
+      <c r="G9" s="78"/>
+      <c r="H9" s="77">
+        <v>10</v>
+      </c>
+      <c r="I9" s="78"/>
+      <c r="J9" s="77">
+        <v>10</v>
+      </c>
+      <c r="K9" s="78"/>
+      <c r="L9" s="77">
+        <v>8</v>
+      </c>
+      <c r="M9" s="78"/>
+      <c r="N9" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="78"/>
+      <c r="P9" s="39">
+        <f>SUM(B9:N9)</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="77">
+        <v>0</v>
+      </c>
+      <c r="C10" s="78"/>
+      <c r="D10" s="77">
+        <v>10</v>
+      </c>
+      <c r="E10" s="78"/>
+      <c r="F10" s="77">
+        <v>10</v>
+      </c>
+      <c r="G10" s="78"/>
+      <c r="H10" s="90">
+        <v>10</v>
+      </c>
+      <c r="I10" s="78"/>
+      <c r="J10" s="77">
+        <v>10</v>
+      </c>
+      <c r="K10" s="78"/>
+      <c r="L10" s="77">
+        <v>8</v>
+      </c>
+      <c r="M10" s="78"/>
+      <c r="N10" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="78"/>
+      <c r="P10" s="39">
+        <f t="shared" ref="P10:P22" si="0">SUM(B10:O10)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="77">
+        <v>10</v>
+      </c>
+      <c r="C11" s="78"/>
+      <c r="D11" s="77">
+        <v>10</v>
+      </c>
+      <c r="E11" s="78"/>
+      <c r="F11" s="91">
+        <v>10</v>
+      </c>
+      <c r="G11" s="78"/>
+      <c r="H11" s="90">
+        <v>10</v>
+      </c>
+      <c r="I11" s="78"/>
+      <c r="J11" s="77">
+        <v>10</v>
+      </c>
+      <c r="K11" s="78"/>
+      <c r="L11" s="92">
+        <v>8</v>
+      </c>
+      <c r="M11" s="93"/>
+      <c r="N11" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" s="78"/>
+      <c r="P11" s="39">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="77">
+        <v>0</v>
+      </c>
+      <c r="C12" s="78"/>
+      <c r="D12" s="77">
+        <v>10</v>
+      </c>
+      <c r="E12" s="78"/>
+      <c r="F12" s="91">
+        <v>10</v>
+      </c>
+      <c r="G12" s="78"/>
+      <c r="H12" s="90">
+        <v>10</v>
+      </c>
+      <c r="I12" s="78"/>
+      <c r="J12" s="77">
+        <v>10</v>
+      </c>
+      <c r="K12" s="78"/>
+      <c r="L12" s="77">
+        <v>8</v>
+      </c>
+      <c r="M12" s="78"/>
+      <c r="N12" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="78"/>
+      <c r="P12" s="39">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="37"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="37"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="37"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="37"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="38"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="38"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="38"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="38"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="38"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="38"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="P23" s="5">
+        <f>SUM(P8:P22)</f>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="21"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="D25" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G25" s="22"/>
+      <c r="J25" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="24"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="24"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J29" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="23"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" s="24"/>
+      <c r="J31" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="K31" s="25"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="24"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="24"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="I80" s="36"/>
+      <c r="J80" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="K80" s="36"/>
+      <c r="L80" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="M80" s="36"/>
+      <c r="N80" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="57">
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="J25:R25"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F11:G11"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="P5:P7"/>
@@ -5814,31 +6901,973 @@
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="L11:M11"/>
     <mergeCell ref="J8:K8"/>
-    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B4:P4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H8:I8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:S80"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="14" width="5.7109375" customWidth="1"/>
+    <col min="15" max="15" width="5.7109375" style="56" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" customWidth="1"/>
+    <col min="17" max="102" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="75"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="71"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="71"/>
+      <c r="B3" s="79" t="str">
+        <f>A80</f>
+        <v>Týden 43</v>
+      </c>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="24"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="71"/>
+      <c r="B4" s="72" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="75"/>
+      <c r="B5" s="80" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="66"/>
+      <c r="D5" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="66"/>
+      <c r="F5" s="81" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="66"/>
+      <c r="H5" s="81" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="66"/>
+      <c r="J5" s="81" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="66"/>
+      <c r="L5" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="66"/>
+      <c r="N5" s="86" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="82" t="str">
+        <f>B80</f>
+        <v>21.10.2024</v>
+      </c>
+      <c r="C6" s="83"/>
+      <c r="D6" s="82" t="str">
+        <f>D80</f>
+        <v>22.10.2024</v>
+      </c>
+      <c r="E6" s="83"/>
+      <c r="F6" s="82" t="str">
+        <f>F80</f>
+        <v>23.10.2024</v>
+      </c>
+      <c r="G6" s="83"/>
+      <c r="H6" s="82" t="str">
+        <f>H80</f>
+        <v>24.10.2024</v>
+      </c>
+      <c r="I6" s="83"/>
+      <c r="J6" s="82" t="str">
+        <f>J80</f>
+        <v>25.10.2024</v>
+      </c>
+      <c r="K6" s="83"/>
+      <c r="L6" s="82" t="str">
+        <f>L80</f>
+        <v>26.10.2024</v>
+      </c>
+      <c r="M6" s="83"/>
+      <c r="N6" s="87">
+        <f>N80</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="83"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="94" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="75"/>
+      <c r="B7" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="N7" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="69"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="77">
+        <v>10</v>
+      </c>
+      <c r="C8" s="78"/>
+      <c r="D8" s="77">
+        <v>8</v>
+      </c>
+      <c r="E8" s="78"/>
+      <c r="F8" s="77">
+        <v>10</v>
+      </c>
+      <c r="G8" s="78"/>
+      <c r="H8" s="77">
+        <v>10</v>
+      </c>
+      <c r="I8" s="78"/>
+      <c r="J8" s="77">
+        <v>7</v>
+      </c>
+      <c r="K8" s="78"/>
+      <c r="L8" s="92">
+        <v>5</v>
+      </c>
+      <c r="M8" s="93"/>
+      <c r="N8" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="78"/>
+      <c r="P8" s="39">
+        <f>SUM(B8:N8)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="77">
+        <v>10</v>
+      </c>
+      <c r="C9" s="78"/>
+      <c r="D9" s="77">
+        <v>10</v>
+      </c>
+      <c r="E9" s="78"/>
+      <c r="F9" s="77">
+        <v>10</v>
+      </c>
+      <c r="G9" s="78"/>
+      <c r="H9" s="77">
+        <v>10</v>
+      </c>
+      <c r="I9" s="78"/>
+      <c r="J9" s="77">
+        <v>7</v>
+      </c>
+      <c r="K9" s="78"/>
+      <c r="L9" s="92">
+        <v>5</v>
+      </c>
+      <c r="M9" s="93"/>
+      <c r="N9" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="78"/>
+      <c r="P9" s="39">
+        <f>SUM(B9:N9)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="77">
+        <v>10</v>
+      </c>
+      <c r="C10" s="78"/>
+      <c r="D10" s="77">
+        <v>10</v>
+      </c>
+      <c r="E10" s="78"/>
+      <c r="F10" s="77">
+        <v>10</v>
+      </c>
+      <c r="G10" s="78"/>
+      <c r="H10" s="77">
+        <v>10</v>
+      </c>
+      <c r="I10" s="78"/>
+      <c r="J10" s="77">
+        <v>7</v>
+      </c>
+      <c r="K10" s="78"/>
+      <c r="L10" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="78"/>
+      <c r="N10" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="78"/>
+      <c r="P10" s="39">
+        <f t="shared" ref="P10:P22" si="0">SUM(B10:O10)</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="77">
+        <v>10</v>
+      </c>
+      <c r="C11" s="78"/>
+      <c r="D11" s="77">
+        <v>10</v>
+      </c>
+      <c r="E11" s="78"/>
+      <c r="F11" s="77">
+        <v>10</v>
+      </c>
+      <c r="G11" s="78"/>
+      <c r="H11" s="77">
+        <v>10</v>
+      </c>
+      <c r="I11" s="78"/>
+      <c r="J11" s="77">
+        <v>7</v>
+      </c>
+      <c r="K11" s="78"/>
+      <c r="L11" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="78"/>
+      <c r="N11" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" s="78"/>
+      <c r="P11" s="39">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="77">
+        <v>10</v>
+      </c>
+      <c r="C12" s="78"/>
+      <c r="D12" s="77">
+        <v>10</v>
+      </c>
+      <c r="E12" s="78"/>
+      <c r="F12" s="77">
+        <v>10</v>
+      </c>
+      <c r="G12" s="78"/>
+      <c r="H12" s="77">
+        <v>10</v>
+      </c>
+      <c r="I12" s="78"/>
+      <c r="J12" s="77">
+        <v>7</v>
+      </c>
+      <c r="K12" s="78"/>
+      <c r="L12" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="78"/>
+      <c r="N12" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="78"/>
+      <c r="P12" s="39">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="77">
+        <v>10</v>
+      </c>
+      <c r="C13" s="78"/>
+      <c r="D13" s="77">
+        <v>10</v>
+      </c>
+      <c r="E13" s="78"/>
+      <c r="F13" s="77">
+        <v>10</v>
+      </c>
+      <c r="G13" s="78"/>
+      <c r="H13" s="77">
+        <v>10</v>
+      </c>
+      <c r="I13" s="78"/>
+      <c r="J13" s="77">
+        <v>7</v>
+      </c>
+      <c r="K13" s="78"/>
+      <c r="L13" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="78"/>
+      <c r="N13" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="78"/>
+      <c r="P13" s="39">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="77">
+        <v>10</v>
+      </c>
+      <c r="C14" s="78"/>
+      <c r="D14" s="77">
+        <v>10</v>
+      </c>
+      <c r="E14" s="78"/>
+      <c r="F14" s="77">
+        <v>10</v>
+      </c>
+      <c r="G14" s="78"/>
+      <c r="H14" s="77">
+        <v>10</v>
+      </c>
+      <c r="I14" s="78"/>
+      <c r="J14" s="77">
+        <v>7</v>
+      </c>
+      <c r="K14" s="78"/>
+      <c r="L14" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="78"/>
+      <c r="N14" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" s="78"/>
+      <c r="P14" s="39">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="77">
+        <v>10</v>
+      </c>
+      <c r="C15" s="78"/>
+      <c r="D15" s="77">
+        <v>10</v>
+      </c>
+      <c r="E15" s="78"/>
+      <c r="F15" s="77">
+        <v>10</v>
+      </c>
+      <c r="G15" s="78"/>
+      <c r="H15" s="77">
+        <v>10</v>
+      </c>
+      <c r="I15" s="78"/>
+      <c r="J15" s="77">
+        <v>7</v>
+      </c>
+      <c r="K15" s="78"/>
+      <c r="L15" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="78"/>
+      <c r="N15" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O15" s="78"/>
+      <c r="P15" s="39">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="77"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="92">
+        <v>5</v>
+      </c>
+      <c r="M16" s="93"/>
+      <c r="N16" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O16" s="78"/>
+      <c r="P16" s="39">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="38"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="38"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="78"/>
+      <c r="N18" s="77"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="38"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="38"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="38"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="38"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="78"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="77"/>
+      <c r="M22" s="78"/>
+      <c r="N22" s="77"/>
+      <c r="O22" s="78"/>
+      <c r="P22" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="P23" s="5">
+        <f>SUM(P8:P22)</f>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="21"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="D25" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G25" s="22"/>
+      <c r="J25" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="24"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="24"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J29" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="23"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" s="24"/>
+      <c r="J31" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="K31" s="25"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="24"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="24"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I80" s="36"/>
+      <c r="J80" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="K80" s="36"/>
+      <c r="L80" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="M80" s="36"/>
+      <c r="N80" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="127">
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="N12:O12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="J25:R25"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="N20:O20"/>
     <mergeCell ref="N11:O11"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F16:G16"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="J29:S29"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J25:R25"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B4:P4"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="L12:M12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
